--- a/docs/範例_使用者帳號管理_批次新增.xlsx
+++ b/docs/範例_使用者帳號管理_批次新增.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\campus-toolkit\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChangCC\workspace\campus-toolkit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB864BFE-F5F5-4F94-A633-2E24091800DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9D8B02-E44C-4504-955A-28FAD283ADF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{0F7DB9C0-03AC-4E98-ACB7-4234628B04E2}"/>
+    <workbookView xWindow="13032" yWindow="0" windowWidth="23532" windowHeight="14280" xr2:uid="{0F7DB9C0-03AC-4E98-ACB7-4234628B04E2}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>電子郵件地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,9 +43,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fake02@fake.edu.tw</t>
-  </si>
-  <si>
     <t>fake03@fake.edu.tw</t>
   </si>
   <si>
@@ -53,9 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fake04@fake.edu.tw</t>
-  </si>
-  <si>
     <t>飛克2號</t>
   </si>
   <si>
@@ -67,6 +61,16 @@
   <si>
     <t>111zzzZZZ</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帳號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fake02</t>
+  </si>
+  <si>
+    <t>fake04</t>
   </si>
 </sst>
 </file>
@@ -112,11 +116,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -137,9 +138,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +178,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -283,7 +284,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,7 +426,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -433,65 +434,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0F4001-4939-4474-861F-107A3544EAD0}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
+      <c r="D3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D5" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/範例_使用者帳號管理_批次新增.xlsx
+++ b/docs/範例_使用者帳號管理_批次新增.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChangCC\workspace\campus-toolkit\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\campus-toolkit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9D8B02-E44C-4504-955A-28FAD283ADF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3343C6-D789-4B64-8E20-C0EE5AC4BE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13032" yWindow="0" windowWidth="23532" windowHeight="14280" xr2:uid="{0F7DB9C0-03AC-4E98-ACB7-4234628B04E2}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{0F7DB9C0-03AC-4E98-ACB7-4234628B04E2}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>電子郵件地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,13 @@
   </si>
   <si>
     <t>fake04</t>
+  </si>
+  <si>
+    <t>飛克5號</t>
+  </si>
+  <si>
+    <t>fake05@fake.edu.tw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -116,8 +123,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -138,9 +148,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -178,7 +188,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -284,7 +294,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -426,7 +436,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -434,14 +444,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0F4001-4939-4474-861F-107A3544EAD0}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,7 +465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -466,7 +476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -477,7 +487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -488,7 +498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -496,6 +506,17 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
         <v>9</v>
       </c>
     </row>
